--- a/research/traditional_assets/database/data/nigeria/nigeria_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_real_estate_operations_services.xlsx
@@ -594,34 +594,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.7129963898916967</v>
+        <v>0.7486437613019891</v>
       </c>
       <c r="J2">
-        <v>0.7129963898916967</v>
+        <v>0.7486437613019891</v>
       </c>
       <c r="K2">
-        <v>0.388</v>
+        <v>0.399</v>
       </c>
       <c r="L2">
-        <v>0.7003610108303249</v>
+        <v>0.7215189873417721</v>
       </c>
       <c r="M2">
-        <v>0.395</v>
+        <v>0.336</v>
       </c>
       <c r="N2">
-        <v>0.1196969696969697</v>
+        <v>0.09767441860465118</v>
       </c>
       <c r="O2">
-        <v>1.018041237113402</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="P2">
-        <v>0.395</v>
+        <v>0.336</v>
       </c>
       <c r="Q2">
-        <v>0.1196969696969697</v>
+        <v>0.09767441860465118</v>
       </c>
       <c r="R2">
-        <v>1.018041237113402</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,31 +630,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.286</v>
+        <v>0.13</v>
       </c>
       <c r="V2">
-        <v>0.08666666666666667</v>
+        <v>0.03779069767441861</v>
       </c>
       <c r="W2">
-        <v>0.06621160409556313</v>
+        <v>0.06903114186851211</v>
       </c>
       <c r="X2">
-        <v>0.07425666123254283</v>
+        <v>0.134136380550374</v>
       </c>
       <c r="Y2">
-        <v>-0.0080450571369797</v>
+        <v>-0.06510523868186191</v>
       </c>
       <c r="Z2">
-        <v>0.09654932032066922</v>
+        <v>0.1006552602839461</v>
       </c>
       <c r="AA2">
-        <v>0.0688393168351342</v>
+        <v>0.07535493265380414</v>
       </c>
       <c r="AB2">
-        <v>0.07425666123254283</v>
+        <v>0.134136380550374</v>
       </c>
       <c r="AC2">
-        <v>-0.005417344397408638</v>
+        <v>-0.05878144789656989</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.286</v>
+        <v>-0.13</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.0948905109489051</v>
+        <v>-0.03927492447129909</v>
       </c>
       <c r="AK2">
-        <v>-0.05205678922460865</v>
+        <v>-0.02402957486136784</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -695,7 +695,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SFS Real Estate investment Trust (NGSE:SFSREIT)</t>
+          <t>SFS Real Estate Investment Trust Fund (NGSE:SFSREIT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,34 +710,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.7129963898916967</v>
+        <v>0.7486437613019891</v>
       </c>
       <c r="J3">
-        <v>0.7129963898916967</v>
+        <v>0.7486437613019891</v>
       </c>
       <c r="K3">
-        <v>0.388</v>
+        <v>0.399</v>
       </c>
       <c r="L3">
-        <v>0.7003610108303249</v>
+        <v>0.7215189873417721</v>
       </c>
       <c r="M3">
-        <v>0.395</v>
+        <v>0.336</v>
       </c>
       <c r="N3">
-        <v>0.1196969696969697</v>
+        <v>0.09767441860465118</v>
       </c>
       <c r="O3">
-        <v>1.018041237113402</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="P3">
-        <v>0.395</v>
+        <v>0.336</v>
       </c>
       <c r="Q3">
-        <v>0.1196969696969697</v>
+        <v>0.09767441860465118</v>
       </c>
       <c r="R3">
-        <v>1.018041237113402</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -746,31 +746,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.286</v>
+        <v>0.13</v>
       </c>
       <c r="V3">
-        <v>0.08666666666666667</v>
+        <v>0.03779069767441861</v>
       </c>
       <c r="W3">
-        <v>0.06621160409556313</v>
+        <v>0.06903114186851211</v>
       </c>
       <c r="X3">
-        <v>0.07425666123254283</v>
+        <v>0.134136380550374</v>
       </c>
       <c r="Y3">
-        <v>-0.0080450571369797</v>
+        <v>-0.06510523868186191</v>
       </c>
       <c r="Z3">
-        <v>0.09654932032066922</v>
+        <v>0.1006552602839461</v>
       </c>
       <c r="AA3">
-        <v>0.0688393168351342</v>
+        <v>0.07535493265380414</v>
       </c>
       <c r="AB3">
-        <v>0.07425666123254283</v>
+        <v>0.134136380550374</v>
       </c>
       <c r="AC3">
-        <v>-0.005417344397408638</v>
+        <v>-0.05878144789656989</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.286</v>
+        <v>-0.13</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0948905109489051</v>
+        <v>-0.03927492447129909</v>
       </c>
       <c r="AK3">
-        <v>-0.05205678922460865</v>
+        <v>-0.02402957486136784</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/nigeria/nigeria_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_real_estate_operations_services.xlsx
@@ -587,6 +587,12 @@
           <t>Real Estate (Operations &amp; Services)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.09119999999999999</v>
+      </c>
+      <c r="E2">
+        <v>0.108</v>
+      </c>
       <c r="G2">
         <v>0</v>
       </c>
@@ -594,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.7486437613019891</v>
+        <v>0.7936117936117937</v>
       </c>
       <c r="J2">
-        <v>0.7486437613019891</v>
+        <v>0.7936117936117937</v>
       </c>
       <c r="K2">
-        <v>0.399</v>
+        <v>0.314</v>
       </c>
       <c r="L2">
-        <v>0.7215189873417721</v>
+        <v>0.7714987714987716</v>
       </c>
       <c r="M2">
-        <v>0.336</v>
+        <v>0.231</v>
       </c>
       <c r="N2">
-        <v>0.09767441860465118</v>
+        <v>0.1013157894736842</v>
       </c>
       <c r="O2">
-        <v>0.8421052631578947</v>
+        <v>0.7356687898089173</v>
       </c>
       <c r="P2">
-        <v>0.336</v>
+        <v>0.231</v>
       </c>
       <c r="Q2">
-        <v>0.09767441860465118</v>
+        <v>0.1013157894736842</v>
       </c>
       <c r="R2">
-        <v>0.8421052631578947</v>
+        <v>0.7356687898089173</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.13</v>
+        <v>0.007</v>
       </c>
       <c r="V2">
-        <v>0.03779069767441861</v>
+        <v>0.003070175438596492</v>
       </c>
       <c r="W2">
-        <v>0.06903114186851211</v>
+        <v>0.05667870036101083</v>
       </c>
       <c r="X2">
-        <v>0.134136380550374</v>
+        <v>0.1248189207944612</v>
       </c>
       <c r="Y2">
-        <v>-0.06510523868186191</v>
+        <v>-0.06814022043345035</v>
       </c>
       <c r="Z2">
-        <v>0.1006552602839461</v>
+        <v>0.07523105360443622</v>
       </c>
       <c r="AA2">
-        <v>0.07535493265380414</v>
+        <v>0.05970425138632163</v>
       </c>
       <c r="AB2">
-        <v>0.134136380550374</v>
+        <v>0.1248189207944612</v>
       </c>
       <c r="AC2">
-        <v>-0.05878144789656989</v>
+        <v>-0.06511466940813955</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.13</v>
+        <v>-0.007</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.03927492447129909</v>
+        <v>-0.003079630444346679</v>
       </c>
       <c r="AK2">
-        <v>-0.02402957486136784</v>
+        <v>-0.002362470469119136</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -703,6 +709,12 @@
           <t>Real Estate (Operations &amp; Services)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.09119999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.108</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -710,34 +722,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.7486437613019891</v>
+        <v>0.7936117936117937</v>
       </c>
       <c r="J3">
-        <v>0.7486437613019891</v>
+        <v>0.7936117936117937</v>
       </c>
       <c r="K3">
-        <v>0.399</v>
+        <v>0.314</v>
       </c>
       <c r="L3">
-        <v>0.7215189873417721</v>
+        <v>0.7714987714987716</v>
       </c>
       <c r="M3">
-        <v>0.336</v>
+        <v>0.231</v>
       </c>
       <c r="N3">
-        <v>0.09767441860465118</v>
+        <v>0.1013157894736842</v>
       </c>
       <c r="O3">
-        <v>0.8421052631578947</v>
+        <v>0.7356687898089173</v>
       </c>
       <c r="P3">
-        <v>0.336</v>
+        <v>0.231</v>
       </c>
       <c r="Q3">
-        <v>0.09767441860465118</v>
+        <v>0.1013157894736842</v>
       </c>
       <c r="R3">
-        <v>0.8421052631578947</v>
+        <v>0.7356687898089173</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -746,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.13</v>
+        <v>0.007</v>
       </c>
       <c r="V3">
-        <v>0.03779069767441861</v>
+        <v>0.003070175438596492</v>
       </c>
       <c r="W3">
-        <v>0.06903114186851211</v>
+        <v>0.05667870036101083</v>
       </c>
       <c r="X3">
-        <v>0.134136380550374</v>
+        <v>0.1248189207944612</v>
       </c>
       <c r="Y3">
-        <v>-0.06510523868186191</v>
+        <v>-0.06814022043345035</v>
       </c>
       <c r="Z3">
-        <v>0.1006552602839461</v>
+        <v>0.07523105360443622</v>
       </c>
       <c r="AA3">
-        <v>0.07535493265380414</v>
+        <v>0.05970425138632163</v>
       </c>
       <c r="AB3">
-        <v>0.134136380550374</v>
+        <v>0.1248189207944612</v>
       </c>
       <c r="AC3">
-        <v>-0.05878144789656989</v>
+        <v>-0.06511466940813955</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -782,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.13</v>
+        <v>-0.007</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -791,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.03927492447129909</v>
+        <v>-0.003079630444346679</v>
       </c>
       <c r="AK3">
-        <v>-0.02402957486136784</v>
+        <v>-0.002362470469119136</v>
       </c>
       <c r="AL3">
         <v>0</v>
